--- a/output/pdf_financials_xlsx/QTRH.xlsx
+++ b/output/pdf_financials_xlsx/QTRH.xlsx
@@ -1058,10 +1058,10 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.428</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.548</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -2008,10 +2008,10 @@
         <v>20.624</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>16.957</v>
+        <v>16.529</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>19.622</v>
+        <v>19.074</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>17.421</v>
@@ -2124,10 +2124,10 @@
         <v>55.763</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>55.121</v>
+        <v>54.693</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>54.273</v>
+        <v>53.725</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>43.4</v>
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>53.5909775898109</v>
+        <v>53.1748578095377</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>58.43597915500237</v>
+        <v>57.84594513114259</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>32.2171166422935</v>
@@ -90727,7 +90727,7 @@
       </c>
       <c r="D826" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E826" t="inlineStr">
@@ -93265,7 +93265,7 @@
       </c>
       <c r="D852" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E852" t="inlineStr">

--- a/output/pdf_financials_xlsx/QTRH.xlsx
+++ b/output/pdf_financials_xlsx/QTRH.xlsx
@@ -2072,19 +2072,19 @@
         <v>34.651</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>25.979</v>
+        <v>1.057</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>27.15</v>
+        <v>1.517</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>21.704</v>
+        <v>1.112</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>21.811</v>
+        <v>23.379</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>16.181</v>
+        <v>29.612</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>11.709</v>
@@ -2130,19 +2130,19 @@
         <v>53.725</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>43.4</v>
+        <v>18.478</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-28.278</v>
+        <v>-53.911</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>39.282</v>
+        <v>18.69</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-4.754</v>
+        <v>-3.186</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>31.083</v>
+        <v>44.514</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-26.004</v>
@@ -2192,19 +2192,19 @@
         <v>57.84594513114259</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>32.2171166422935</v>
+        <v>13.71677145890091</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-36.53441170010723</v>
+        <v>-69.65155488947171</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>26.77344601962923</v>
+        <v>12.73854961832061</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>-22638.09523809524</v>
+        <v>-15171.42857142857</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>518050</v>
+        <v>741900</v>
       </c>
       <c r="P30" s="3" t="n">
         <v>-18.05996374672714</v>
@@ -6321,10 +6321,10 @@
         <v>21.704</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>21.811</v>
+        <v>1.568</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>16.181</v>
+        <v>2.535</v>
       </c>
       <c r="P100" s="3" t="n">
         <v>11.709</v>
@@ -47304,7 +47304,11 @@
           <t>Depreciation of right-of-use assets 8</t>
         </is>
       </c>
-      <c r="D391" t="inlineStr"/>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E391" t="inlineStr">
         <is>
           <t>-</t>
@@ -75775,7 +75779,11 @@
           <t>Depreciation of right-of-use assets 8</t>
         </is>
       </c>
-      <c r="D676" t="inlineStr"/>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E676" t="inlineStr">
         <is>
           <t>-</t>
@@ -75874,7 +75882,11 @@
           <t>Depreciation of property, plant and equipment 9</t>
         </is>
       </c>
-      <c r="D677" t="inlineStr"/>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E677" t="inlineStr">
         <is>
           <t>-</t>
@@ -75975,7 +75987,7 @@
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
@@ -78056,7 +78068,11 @@
           <t>Depreciation of right-of-use assets 9</t>
         </is>
       </c>
-      <c r="D699" t="inlineStr"/>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E699" t="inlineStr">
         <is>
           <t>-</t>
@@ -78155,7 +78171,11 @@
           <t>Depreciation of property, plant and equipment 10</t>
         </is>
       </c>
-      <c r="D700" t="inlineStr"/>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E700" t="inlineStr">
         <is>
           <t>-</t>
@@ -78256,7 +78276,7 @@
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
@@ -84666,7 +84686,11 @@
           <t>Depreciation of right-of-use assets 8</t>
         </is>
       </c>
-      <c r="D765" t="inlineStr"/>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E765" t="inlineStr">
         <is>
           <t>-</t>
@@ -84765,7 +84789,11 @@
           <t>Depreciation of property, plant and equipment 9</t>
         </is>
       </c>
-      <c r="D766" t="inlineStr"/>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E766" t="inlineStr">
         <is>
           <t>-</t>
@@ -84866,7 +84894,7 @@
       </c>
       <c r="D767" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E767" t="inlineStr">
@@ -87771,7 +87799,11 @@
           <t>Depreciation of property, plant and equipment (Note 9)</t>
         </is>
       </c>
-      <c r="D796" t="inlineStr"/>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E796" t="inlineStr">
         <is>
           <t>-</t>
